--- a/diseases/d064/2000-2004.xlsx
+++ b/diseases/d064/2000-2004.xlsx
@@ -2309,6 +2309,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2450,6 +2455,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2591,6 +2601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2732,6 +2747,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2873,6 +2893,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3014,6 +3039,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3155,6 +3185,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3296,6 +3331,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3437,6 +3477,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3578,6 +3623,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3719,6 +3769,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3860,6 +3915,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4771,6 +4831,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4912,6 +4977,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5053,6 +5123,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5194,6 +5269,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5335,6 +5415,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5476,6 +5561,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5617,6 +5707,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5758,6 +5853,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5899,6 +5999,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6040,6 +6145,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6181,6 +6291,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6322,6 +6437,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7233,6 +7353,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7374,6 +7499,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7515,6 +7645,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7656,6 +7791,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7797,6 +7937,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7938,6 +8083,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8079,6 +8229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8220,6 +8375,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8361,6 +8521,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8502,6 +8667,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8643,6 +8813,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8782,6 +8957,11 @@
       <c r="S53" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">

--- a/diseases/d064/2000-2004.xlsx
+++ b/diseases/d064/2000-2004.xlsx
@@ -764,11 +764,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
@@ -786,12 +781,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -802,11 +792,6 @@
       <c r="AT2" t="n">
         <v>1</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -829,22 +814,22 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -871,7 +856,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -902,12 +887,12 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2000-01</t>
+          <t>2001-01</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -916,99 +901,19 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Bólusótt</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN3" t="b">
-        <v>1</v>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1016,12 +921,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1032,11 +932,6 @@
       <c r="AT3" t="n">
         <v>1</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -1059,22 +954,22 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1001,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1132,12 +1027,12 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2001-01</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1156,7 +1051,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1181,7 +1076,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
         </is>
       </c>
       <c r="AT4" t="n">
@@ -1194,42 +1089,42 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1156,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1287,12 +1182,12 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2001-01</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1303,22 +1198,22 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_HISTORY</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Bólusótt</t>
+          <t>Smallpox</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1328,7 +1223,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>national_registry_notifications</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1343,7 +1238,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1368,7 +1263,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1378,12 +1273,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1411,7 +1306,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
         </is>
       </c>
       <c r="AT5" t="n">
@@ -1424,42 +1319,42 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1386,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1534,14 +1429,9 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1556,65 +1446,55 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1641,17 +1521,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1686,165 +1566,66 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="R7" t="n">
+        <v>0</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN7" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -1876,12 +1657,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1902,12 +1683,12 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-02-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2002-02</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1919,87 +1700,63 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -2026,17 +1783,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2057,12 +1814,12 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-03-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2002-03</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2071,165 +1828,66 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Bólusótt</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
+      <c r="R9" t="n">
+        <v>0</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN9" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -2287,12 +1945,12 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-04-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2002-04</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2304,11 +1962,6 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2321,22 +1974,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2433,12 +2076,12 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2002-02-01</t>
+          <t>2002-05-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2002-02</t>
+          <t>2002-05</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2450,11 +2093,6 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2467,22 +2105,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2579,12 +2207,12 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2002-03-01</t>
+          <t>2002-06-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2002-03</t>
+          <t>2002-06</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2596,11 +2224,6 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2613,22 +2236,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2725,12 +2338,12 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2002-04-01</t>
+          <t>2002-07-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-07</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2742,11 +2355,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2759,22 +2367,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2871,12 +2469,12 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2002-05-01</t>
+          <t>2002-08-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2002-05</t>
+          <t>2002-08</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2888,11 +2486,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2905,22 +2498,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -3017,12 +2600,12 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2002-06-01</t>
+          <t>2002-09-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2002-06</t>
+          <t>2002-09</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3034,11 +2617,6 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3051,22 +2629,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3163,12 +2731,12 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2002-07-01</t>
+          <t>2002-10-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2002-07</t>
+          <t>2002-10</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3180,11 +2748,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3197,22 +2760,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3309,12 +2862,12 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2002-08-01</t>
+          <t>2002-11-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2002-08</t>
+          <t>2002-11</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3326,11 +2879,6 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3343,22 +2891,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3455,12 +2993,12 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2002-09-01</t>
+          <t>2002-12-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2002-09</t>
+          <t>2002-12</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3472,11 +3010,6 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3489,22 +3022,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3575,12 +3098,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3601,12 +3124,12 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2002-10-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2002-10</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3623,73 +3146,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3716,17 +3248,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3747,12 +3279,12 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2002-11-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2002-11</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3761,81 +3293,165 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN20" t="b">
+        <v>1</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3867,12 +3483,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3893,12 +3509,12 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2002-12</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3910,78 +3526,72 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr"/>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -4013,12 +3623,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -4056,87 +3666,63 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -4163,17 +3749,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4194,12 +3780,12 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2003-02-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2003-02</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4208,165 +3794,66 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="R23" t="n">
+        <v>0</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN23" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -4398,12 +3885,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4424,12 +3911,12 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2003-03-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2003-03</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4441,87 +3928,63 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -4548,17 +4011,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4579,12 +4042,12 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2003-04-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2003-04</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4593,165 +4056,66 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Bólusótt</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
+      <c r="R25" t="n">
+        <v>0</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN25" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -4809,12 +4173,12 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2003-05-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2003-05</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4826,11 +4190,6 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4843,22 +4202,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4955,12 +4304,12 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2003-02-01</t>
+          <t>2003-06-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2003-02</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4972,11 +4321,6 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4989,22 +4333,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -5101,12 +4435,12 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2003-03-01</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2003-03</t>
+          <t>2003-07</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -5118,11 +4452,6 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5135,22 +4464,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -5247,12 +4566,12 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2003-04-01</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2003-04</t>
+          <t>2003-08</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5264,11 +4583,6 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5281,22 +4595,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5393,12 +4697,12 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2003-05-01</t>
+          <t>2003-09-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2003-05</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5410,11 +4714,6 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5427,22 +4726,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5539,12 +4828,12 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2003-06-01</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -5556,11 +4845,6 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5573,22 +4857,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5685,12 +4959,12 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2003-07</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5702,11 +4976,6 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5719,22 +4988,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5831,12 +5090,12 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2003-08</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5848,11 +5107,6 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5865,22 +5119,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5951,12 +5195,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5977,12 +5221,12 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2003-09-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2003-09</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5999,73 +5243,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6092,17 +5345,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -6123,12 +5376,12 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -6137,81 +5390,165 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6243,12 +5580,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -6269,12 +5606,12 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6286,78 +5623,72 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6415,12 +5746,12 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6432,11 +5763,6 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6449,22 +5775,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6535,12 +5851,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -6561,12 +5877,12 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6578,87 +5894,63 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ38" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -6685,17 +5977,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6716,12 +6008,12 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6730,165 +6022,66 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="R39" t="n">
+        <v>0</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG39" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN39" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -6920,12 +6113,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6946,12 +6139,12 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6963,87 +6156,63 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7070,17 +6239,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -7101,12 +6270,12 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -7115,165 +6284,66 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>Bólusótt</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
+      <c r="R41" t="n">
+        <v>0</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG41" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN41" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7331,12 +6401,12 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -7348,11 +6418,6 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7365,22 +6430,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7477,12 +6532,12 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7494,11 +6549,6 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7511,22 +6561,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7623,12 +6663,12 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7640,11 +6680,6 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7657,22 +6692,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7769,12 +6794,12 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2004-09-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-09</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7786,11 +6811,6 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7803,22 +6823,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7915,12 +6925,12 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-10-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-10</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7932,11 +6942,6 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7949,22 +6954,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -8061,12 +7056,12 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-11-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-11</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -8078,11 +7073,6 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8095,22 +7085,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -8207,12 +7187,12 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-12-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-12</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -8224,11 +7204,6 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8241,23 +7216,13 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -8294,736 +7259,6 @@
         </is>
       </c>
       <c r="BC48" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>smallpox</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>天花</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>2004-08-01</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2004-08</t>
-        </is>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP49" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
-      <c r="AT49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV49" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA49" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB49" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC49" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>smallpox</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>天花</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>2004-09-01</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2004-09</t>
-        </is>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP50" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
-      <c r="AT50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV50" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA50" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB50" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC50" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>smallpox</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>天花</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>2004-10-01</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>2004-10</t>
-        </is>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP51" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr"/>
-      <c r="AT51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV51" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA51" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB51" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC51" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>smallpox</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>天花</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>2004-11-01</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>2004-11</t>
-        </is>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP52" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
-      <c r="AT52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV52" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA52" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB52" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC52" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>smallpox</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>天花</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>2004-12-01</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>2004-12</t>
-        </is>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP53" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
-      <c r="AT53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV53" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA53" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB53" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC53" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -9155,7 +7390,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -9175,7 +7410,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -9185,7 +7420,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d064/2000-2004.xlsx
+++ b/diseases/d064/2000-2004.xlsx
@@ -764,6 +764,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
@@ -781,7 +786,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -792,6 +802,11 @@
       <c r="AT2" t="n">
         <v>1</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -814,22 +829,22 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -856,7 +871,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -887,12 +902,12 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2001-01</t>
+          <t>2000-01</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -901,19 +916,99 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Bólusótt</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -921,7 +1016,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -932,6 +1032,11 @@
       <c r="AT3" t="n">
         <v>1</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -954,22 +1059,22 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1106,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1027,12 +1132,12 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2001-01</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1051,7 +1156,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1076,7 +1181,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
       <c r="AT4" t="n">
@@ -1089,42 +1194,42 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1261,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1182,12 +1287,12 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2001-01</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1198,22 +1303,22 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
+          <t>SRC_IS_DOH_HISTORY</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Smallpox</t>
+          <t>Bólusótt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1223,7 +1328,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
+          <t>national_registry_notifications</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1238,7 +1343,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>country:CA:national</t>
+          <t>country:IS:national</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1263,7 +1368,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>historical</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1273,12 +1378,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+          <t>IS_DOH_historical_registry_annual</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1306,7 +1411,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
       <c r="AT5" t="n">
@@ -1319,42 +1424,42 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1491,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1429,9 +1534,14 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1446,55 +1556,65 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
         </is>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1641,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1566,66 +1686,165 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1876,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1683,12 +1902,12 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2002-02-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2002-02</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1700,63 +1919,87 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1783,17 +2026,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1814,12 +2057,12 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2002-03-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2002-03</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1828,66 +2071,165 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Bólusótt</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>1</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1945,12 +2287,12 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2002-04-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2076,12 +2418,12 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2002-05-01</t>
+          <t>2002-02-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2002-05</t>
+          <t>2002-02</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2207,12 +2549,12 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2002-06-01</t>
+          <t>2002-03-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2002-06</t>
+          <t>2002-03</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2338,12 +2680,12 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2002-07-01</t>
+          <t>2002-04-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2002-07</t>
+          <t>2002-04</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2469,12 +2811,12 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2002-08-01</t>
+          <t>2002-05-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2002-08</t>
+          <t>2002-05</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2600,12 +2942,12 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2002-09-01</t>
+          <t>2002-06-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2002-09</t>
+          <t>2002-06</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2731,12 +3073,12 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2002-10-01</t>
+          <t>2002-07-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2002-10</t>
+          <t>2002-07</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -2862,12 +3204,12 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2002-11-01</t>
+          <t>2002-08-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2002-11</t>
+          <t>2002-08</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -2993,12 +3335,12 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-09-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2002-12</t>
+          <t>2002-09</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3098,12 +3440,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3124,12 +3466,12 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2002-10-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2002-10</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3141,87 +3483,63 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -3248,17 +3566,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3279,12 +3597,12 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2002-11-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2002-11</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3293,165 +3611,66 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="R20" t="n">
+        <v>0</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN20" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -3483,12 +3702,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3509,12 +3728,12 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2002-12-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2002-12</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3526,19 +3745,14 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
@@ -3546,52 +3760,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+      <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -3623,12 +3833,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3666,63 +3876,87 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3749,17 +3983,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3780,12 +4014,12 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2003-02-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2003-02</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -3794,66 +4028,165 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN23" t="b">
+        <v>1</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3885,12 +4218,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3911,12 +4244,12 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2003-03-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2003-03</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -3928,63 +4261,87 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -4011,17 +4368,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4042,12 +4399,12 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2003-04-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2003-04</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4056,66 +4413,165 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Bólusótt</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN25" t="b">
+        <v>1</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -4173,12 +4629,12 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2003-05-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2003-05</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4304,12 +4760,12 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2003-06-01</t>
+          <t>2003-02-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-02</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4435,12 +4891,12 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2003-03-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2003-07</t>
+          <t>2003-03</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4566,12 +5022,12 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2003-04-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2003-08</t>
+          <t>2003-04</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -4697,12 +5153,12 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2003-09-01</t>
+          <t>2003-05-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2003-09</t>
+          <t>2003-05</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -4828,12 +5284,12 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2003-06-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -4959,12 +5415,12 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2003-07</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5090,12 +5546,12 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2003-08</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5195,12 +5651,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5221,12 +5677,12 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-09-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5238,87 +5694,63 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -5345,17 +5777,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5376,12 +5808,12 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5390,165 +5822,66 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="R35" t="n">
+        <v>0</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN35" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -5580,12 +5913,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5606,12 +5939,12 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -5623,19 +5956,14 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
@@ -5643,52 +5971,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS36" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+      <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -5746,12 +6070,12 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -5851,12 +6175,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5877,12 +6201,12 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -5894,63 +6218,87 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5977,17 +6325,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6008,12 +6356,12 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6022,66 +6370,165 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="R39" t="n">
-        <v>0</v>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN39" t="b">
+        <v>1</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6560,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6139,12 +6586,12 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6156,63 +6603,87 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -6239,17 +6710,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6270,12 +6741,12 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6284,66 +6755,165 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="R41" t="n">
-        <v>0</v>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Bólusótt</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN41" t="b">
+        <v>1</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -6401,12 +6971,12 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6532,12 +7102,12 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -6663,12 +7233,12 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -6794,12 +7364,12 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -6925,12 +7495,12 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7056,12 +7626,12 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7187,12 +7757,12 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -7259,6 +7829,661 @@
         </is>
       </c>
       <c r="BC48" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2004-08-01</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2004-08</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2004-09</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2004-10-01</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2004-10</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2004-11</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -7390,7 +8615,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -7410,7 +8635,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -7420,7 +8645,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d064/2000-2004.xlsx
+++ b/diseases/d064/2000-2004.xlsx
@@ -2304,6 +2304,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2316,12 +2321,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2435,6 +2450,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2447,12 +2467,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2566,6 +2596,11 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2578,12 +2613,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2697,6 +2742,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2709,12 +2759,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2828,6 +2888,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2840,12 +2905,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2959,6 +3034,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2971,12 +3051,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3090,6 +3180,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3102,12 +3197,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3221,6 +3326,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3233,12 +3343,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3352,6 +3472,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3364,12 +3489,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3483,6 +3618,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3495,12 +3635,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3614,6 +3764,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3626,12 +3781,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3745,6 +3910,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3757,12 +3927,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -4646,6 +4826,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4658,12 +4843,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4777,6 +4972,11 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4789,12 +4989,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4908,6 +5118,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4920,12 +5135,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -5039,6 +5264,11 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5051,12 +5281,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5170,6 +5410,11 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5182,12 +5427,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5301,6 +5556,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5313,12 +5573,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5432,6 +5702,11 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5444,12 +5719,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5563,6 +5848,11 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5575,12 +5865,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5694,6 +5994,11 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5706,12 +6011,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5825,6 +6140,11 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5837,12 +6157,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5956,6 +6286,11 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5968,12 +6303,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6087,6 +6432,11 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6099,12 +6449,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6988,6 +7348,11 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7000,12 +7365,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7119,6 +7494,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7131,12 +7511,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7250,6 +7640,11 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7262,12 +7657,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7381,6 +7786,11 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7393,12 +7803,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7512,6 +7932,11 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7524,12 +7949,22 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7643,6 +8078,11 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7655,12 +8095,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7774,6 +8224,11 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7786,12 +8241,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7905,6 +8370,11 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7917,12 +8387,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8036,6 +8516,11 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8048,12 +8533,22 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8167,6 +8662,11 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8179,12 +8679,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8298,6 +8808,11 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8310,12 +8825,22 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8429,6 +8954,11 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8441,12 +8971,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
